--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>706.84</v>
+        <v>694.21</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9717.25</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1282.48</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>37341.92</v>
+        <v>37633.13</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31568.74</v>
+        <v>31632.24</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10309.17</v>
+        <v>10269.21</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>359291.68</v>
+        <v>361779.55</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>26438.82</v>
+        <v>26621.89</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8040.16</v>
+        <v>8014.09</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1172.14</v>
+        <v>1161.2</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10309.17</v>
+        <v>10321.26</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>158713.19</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9421.290000000001</v>
+        <v>9494.969999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7250.94</v>
+        <v>7328.32</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3509.62</v>
+        <v>3547.07</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1250,7 +1294,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1373053-6-CM26</t>
+          <t>1395481-2-SE26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1309,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1319,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.908.116-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1298,20 +1342,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9494.969999999999</v>
+        <v>117272.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>550716-6-CM26</t>
+          <t>1395481-3-SE26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,22 +1374,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.908.116-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>JUNTA NACIONAL DE AUXILIO ESCOLAR Y BECA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1359,74 +1407,212 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7328.32</v>
+        <v>257795.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>1373053-6-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>82.174.900-k</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>9494.969999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>550716-6-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>65.961.370-0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>7328.32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>1495206-3-CM26</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2239-12-LR23</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>may-2026</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>61.981.340-5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>3547.07</v>
       </c>
     </row>
